--- a/Input/Api_template.xlsx
+++ b/Input/Api_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sathanantham.aru\PycharmProjects\ai-accelerator\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3745392-938C-422E-922E-CC826E63B30E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA4E8320-BB85-4A5A-8403-406A041D0A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E9726AB4-B9A0-495D-98A0-366EAEA04346}"/>
   </bookViews>
@@ -36,73 +36,109 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>API Name</t>
-  </si>
-  <si>
-    <t>Method</t>
-  </si>
-  <si>
-    <t>Base URL</t>
-  </si>
-  <si>
-    <t>Endpoint</t>
-  </si>
-  <si>
-    <t>Headers (JSON)</t>
-  </si>
-  <si>
-    <t>Payload (JSON)</t>
-  </si>
-  <si>
-    <t>Auth Required</t>
-  </si>
-  <si>
-    <t>Auth Type</t>
-  </si>
-  <si>
-    <t>Auth Key Name</t>
-  </si>
-  <si>
-    <t>Config Key</t>
-  </si>
-  <si>
-    <t>Login API</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
   <si>
     <t>POST</t>
   </si>
   <si>
-    <t>https://api.example.com</t>
-  </si>
-  <si>
-    <t>/login</t>
-  </si>
-  <si>
-    <t>{"Content-Type":"application/json"}</t>
-  </si>
-  <si>
-    <t>{"username":"test","password":"abc"}</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Bearer</t>
-  </si>
-  <si>
-    <t>Authorization</t>
-  </si>
-  <si>
-    <t>LOGIN_TOKEN</t>
+    <t>Test_Case_Name</t>
+  </si>
+  <si>
+    <t>httpMethod</t>
+  </si>
+  <si>
+    <t>endPoint</t>
+  </si>
+  <si>
+    <t>headers-Authorization</t>
+  </si>
+  <si>
+    <t>Request-username</t>
+  </si>
+  <si>
+    <t>Request-password</t>
+  </si>
+  <si>
+    <t>Expected-StatusCode</t>
+  </si>
+  <si>
+    <t>Expected-Message</t>
+  </si>
+  <si>
+    <t>Validate?</t>
+  </si>
+  <si>
+    <t>Performance?</t>
+  </si>
+  <si>
+    <t>Extract-token</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>GET</t>
+  </si>
+  <si>
+    <t>BodyFormat</t>
+  </si>
+  <si>
+    <t>application/json</t>
+  </si>
+  <si>
+    <t>No_data</t>
+  </si>
+  <si>
+    <t>baseUrl</t>
+  </si>
+  <si>
+    <t>https://reqres.in/</t>
+  </si>
+  <si>
+    <t>headers</t>
+  </si>
+  <si>
+    <t>api/users</t>
+  </si>
+  <si>
+    <t>eve.holt@reqres.in</t>
+  </si>
+  <si>
+    <t>pistol</t>
+  </si>
+  <si>
+    <t>auth_type</t>
+  </si>
+  <si>
+    <t>api/users/2</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>TC_001_check_first_name</t>
+  </si>
+  <si>
+    <t>first_name:Janet</t>
+  </si>
+  <si>
+    <t>first_name:John</t>
+  </si>
+  <si>
+    <t>{
+  "name": "John Doe",
+  "job": "Developer"
+}</t>
+  </si>
+  <si>
+    <t>TC_002_User Creation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -118,6 +154,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -127,7 +177,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -135,11 +185,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -147,8 +213,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -481,74 +560,173 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E797493-FAB4-4293-BFA2-CFB269A5F22C}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.08984375" customWidth="1"/>
+    <col min="4" max="4" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.36328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="2" t="s">
+    <row r="2" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="C2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="2">
+        <v>200</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2"/>
+    </row>
+    <row r="3" spans="1:15" ht="116" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="D3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="2">
+        <v>200</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O3" s="2"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{0A6CFC25-F437-4331-A814-B5AE828D2C60}"/>
+    <hyperlink ref="I2" r:id="rId2" xr:uid="{63BE9794-B0C1-40E3-8C0D-497C56905399}"/>
+    <hyperlink ref="C3" r:id="rId3" xr:uid="{B9686058-62FC-4618-BEB4-BF6C8C7AA825}"/>
+    <hyperlink ref="I3" r:id="rId4" xr:uid="{35B2D983-974C-43E0-90C4-4ADF6EEE27B9}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>